--- a/Testdata/MultipleDistrictTestData.xlsx
+++ b/Testdata/MultipleDistrictTestData.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="MultipleDistrict" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Support Admin</t>
   </si>
   <si>
-    <t xml:space="preserve">Test_RE_Demo_01_Distrct</t>
+    <t xml:space="preserve">DelTest_RE _Demo_0101_Distrct</t>
   </si>
   <si>
     <t xml:space="preserve">testfirst1</t>
@@ -46,13 +46,13 @@
     <t xml:space="preserve">testlast1</t>
   </si>
   <si>
-    <t xml:space="preserve">testredc1@yopmail.com</t>
+    <t xml:space="preserve">testdeldistrictre0101@yopmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">Sunil Game</t>
   </si>
   <si>
-    <t xml:space="preserve">Test_RE_Demo_02_Distrct</t>
+    <t xml:space="preserve">DelTest_RE _Demo_0202_Distrct</t>
   </si>
   <si>
     <t xml:space="preserve">testfirst2</t>
@@ -61,10 +61,10 @@
     <t xml:space="preserve">testlast2</t>
   </si>
   <si>
-    <t xml:space="preserve">testredc2@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_RE_Demo_03_Distrct</t>
+    <t xml:space="preserve">testdeldistrictre0202@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE _Demo_03_Distrct</t>
   </si>
   <si>
     <t xml:space="preserve">testfirst3</t>
@@ -73,10 +73,10 @@
     <t xml:space="preserve">testlast3</t>
   </si>
   <si>
-    <t xml:space="preserve">testredc3@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_RE_Demo_04_Distrct</t>
+    <t xml:space="preserve">testdeldistrictre03@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE _Demo_04_Distrct</t>
   </si>
   <si>
     <t xml:space="preserve">testfirst4</t>
@@ -85,10 +85,10 @@
     <t xml:space="preserve">testlast4</t>
   </si>
   <si>
-    <t xml:space="preserve">testredc4@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_RE_Demo_05_Distrct</t>
+    <t xml:space="preserve">testdeldistrictre04@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE _Demo_05_Distrct</t>
   </si>
   <si>
     <t xml:space="preserve">testfirst5</t>
@@ -97,10 +97,10 @@
     <t xml:space="preserve">testlast5</t>
   </si>
   <si>
-    <t xml:space="preserve">testredc5@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_RE_Demo_06_Distrct</t>
+    <t xml:space="preserve">testdeldistrictre05@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE _Demo_06_Distrct</t>
   </si>
   <si>
     <t xml:space="preserve">testfirst6</t>
@@ -109,10 +109,10 @@
     <t xml:space="preserve">testlast6</t>
   </si>
   <si>
-    <t xml:space="preserve">testredc6@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_RE_Demo_07_Distrct</t>
+    <t xml:space="preserve">testdeldistrictre06@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE _Demo_07_Distrct</t>
   </si>
   <si>
     <t xml:space="preserve">testfirst7</t>
@@ -121,10 +121,10 @@
     <t xml:space="preserve">testlast7</t>
   </si>
   <si>
-    <t xml:space="preserve">testredc7@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_RE_Demo_08_Distrct</t>
+    <t xml:space="preserve">testdeldistrictre07@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE _Demo_08_Distrct</t>
   </si>
   <si>
     <t xml:space="preserve">testfirst8</t>
@@ -133,10 +133,10 @@
     <t xml:space="preserve">testlast8</t>
   </si>
   <si>
-    <t xml:space="preserve">testredc8@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_RE_Demo_09_Distrct</t>
+    <t xml:space="preserve">testdeldistrictre08@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE _Demo_09_Distrct</t>
   </si>
   <si>
     <t xml:space="preserve">testfirst9</t>
@@ -145,10 +145,10 @@
     <t xml:space="preserve">testlast9</t>
   </si>
   <si>
-    <t xml:space="preserve">testredc9@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_RE_Demo_10_Distrct</t>
+    <t xml:space="preserve">testdeldistrictre09@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE _Demo_10_Distrct</t>
   </si>
   <si>
     <t xml:space="preserve">testfirst10</t>
@@ -157,7 +157,7 @@
     <t xml:space="preserve">testlast10</t>
   </si>
   <si>
-    <t xml:space="preserve">testredc10@yopmail.com</t>
+    <t xml:space="preserve">testdeldistrictre10@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -253,25 +253,33 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -397,13 +405,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="23.84765625" defaultRowHeight="20.45" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="33.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.91"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="23.85"/>
   </cols>
@@ -595,19 +603,38 @@
         <v>9</v>
       </c>
     </row>
+    <row r="15" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D22" s="6"/>
+    </row>
+    <row r="23" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D24" s="6"/>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="testredc1@yopmail.com"/>
-    <hyperlink ref="D3" r:id="rId2" display="testredc2@yopmail.com"/>
-    <hyperlink ref="D4" r:id="rId3" display="testredc3@yopmail.com"/>
-    <hyperlink ref="D5" r:id="rId4" display="testredc4@yopmail.com"/>
-    <hyperlink ref="D6" r:id="rId5" display="testredc5@yopmail.com"/>
-    <hyperlink ref="D7" r:id="rId6" display="testredc6@yopmail.com"/>
-    <hyperlink ref="D8" r:id="rId7" display="testredc7@yopmail.com"/>
-    <hyperlink ref="D9" r:id="rId8" display="testredc8@yopmail.com"/>
-    <hyperlink ref="D10" r:id="rId9" display="testredc9@yopmail.com"/>
-    <hyperlink ref="D11" r:id="rId10" display="testredc10@yopmail.com"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/Testdata/MultipleDistrictTestData.xlsx
+++ b/Testdata/MultipleDistrictTestData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
   <si>
     <t xml:space="preserve">District Name</t>
   </si>
@@ -37,127 +37,187 @@
     <t xml:space="preserve">Support Admin</t>
   </si>
   <si>
-    <t xml:space="preserve">DelTest_RE _Demo_0101_Distrct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testfirst1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testlast1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testdeldistrictre0101@yopmail.com</t>
+    <t xml:space="preserve">DelTest_RE_Demo_11_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre11@yopmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">Sunil Game</t>
   </si>
   <si>
-    <t xml:space="preserve">DelTest_RE _Demo_0202_Distrct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testfirst2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testlast2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testdeldistrictre0202@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DelTest_RE _Demo_03_Distrct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testfirst3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testlast3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testdeldistrictre03@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DelTest_RE _Demo_04_Distrct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testfirst4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testlast4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testdeldistrictre04@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DelTest_RE _Demo_05_Distrct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testfirst5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testlast5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testdeldistrictre05@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DelTest_RE _Demo_06_Distrct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testfirst6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testlast6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testdeldistrictre06@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DelTest_RE _Demo_07_Distrct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testfirst7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testlast7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testdeldistrictre07@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DelTest_RE _Demo_08_Distrct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testfirst8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testlast8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testdeldistrictre08@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DelTest_RE _Demo_09_Distrct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testfirst9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testlast9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testdeldistrictre09@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DelTest_RE _Demo_10_Distrct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testfirst10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testlast10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testdeldistrictre10@yopmail.com</t>
+    <t xml:space="preserve">DelTest_RE_Demo_12_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre12@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_13_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre13@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_14_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre14@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_15_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre15@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_16_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre16@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_17_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre17@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_18_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre18@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_19_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre19@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_20_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre20@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_21_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre21@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_22_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre22@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_23_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre23@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_24_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre24@yopmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DelTest_RE_Demo_25_Distrct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testfirst25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testlast25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">testdeldistrictre25@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -167,7 +227,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -196,20 +256,19 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -253,7 +312,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -266,6 +325,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -274,7 +337,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -437,16 +504,16 @@
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -454,16 +521,16 @@
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -471,16 +538,16 @@
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -488,151 +555,237 @@
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5"/>
+      <c r="A15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D16" s="6"/>
+      <c r="A16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5"/>
-      <c r="D17" s="6"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D18" s="6"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D19" s="6"/>
+      <c r="D19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D20" s="6"/>
+      <c r="D20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D21" s="6"/>
+      <c r="D21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D22" s="6"/>
+      <c r="D22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D23" s="6"/>
+      <c r="D23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="20.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D24" s="6"/>
+      <c r="D24" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
